--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484071_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484071_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2547</v>
+        <v>3.5998</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2102</v>
+        <v>4.4993</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9556</v>
+        <v>-0.8994</v>
       </c>
       <c r="G2" t="n">
         <v>1.7213</v>
@@ -610,13 +610,13 @@
         <v>1.7855</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2006</v>
+        <v>0.1446</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3173</v>
+        <v>-0.0283</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1167</v>
+        <v>0.1728</v>
       </c>
       <c r="V2" t="n">
         <v>0.9405</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. FABREGAS CANALS</t>
+          <t>G. GUTIÉRREZ MONREAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0528</v>
+        <v>2.8532</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2183</v>
+        <v>2.7561</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2711</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3931</v>
+        <v>2.7441</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4633</v>
+        <v>-0.0257</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8564000000000001</v>
+        <v>2.7698</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.5666</v>
+        <v>4.9982</v>
       </c>
       <c r="K3" t="n">
-        <v>0.711</v>
+        <v>1.9758</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.2775</v>
+        <v>3.0223</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1735</v>
+        <v>-2.2541</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2477</v>
+        <v>-2.0015</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4211</v>
+        <v>-0.2526</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5871</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5871</v>
+        <v>1.7855</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2556</v>
+        <v>0.2877</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.255</v>
+        <v>0.1304</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.1572</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6032</v>
+        <v>1.0118</v>
       </c>
       <c r="W3" t="n">
         <v>0.6032</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. NGOMO MIFUMU</t>
+          <t>G. FABREGAS CANALS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6286</v>
+        <v>2.218</v>
       </c>
       <c r="E4" t="n">
-        <v>3.723</v>
+        <v>0.0311</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.0944</v>
+        <v>2.187</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.2997</v>
+        <v>-0.3931</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4338</v>
+        <v>0.4633</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.7334</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5609</v>
+        <v>-0.5666</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4353</v>
+        <v>0.711</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1256</v>
+        <v>-1.2775</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.8605</v>
+        <v>0.1735</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.0015</v>
+        <v>-0.2477</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.859</v>
+        <v>0.4211</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7935</v>
+        <v>1.5871</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7855</v>
+        <v>1.5871</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1347</v>
+        <v>0.4208</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1541</v>
+        <v>-0.0056</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0193</v>
+        <v>0.4264</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. GUTIÉRREZ MONREAL</t>
+          <t>A. GARCIA MARTINEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3044</v>
+        <v>0.5032</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6281</v>
+        <v>-0.7008</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3237</v>
+        <v>1.204</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7441</v>
+        <v>-0.6351</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0257</v>
+        <v>-1.371</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7698</v>
+        <v>0.7359</v>
       </c>
       <c r="J5" t="n">
-        <v>4.9982</v>
+        <v>0.257</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9758</v>
+        <v>-0.589</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0223</v>
+        <v>0.8459</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.2541</v>
+        <v>-0.8921</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.0015</v>
+        <v>-0.782</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2526</v>
+        <v>-0.11</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
         <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2611</v>
+        <v>0.9479</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9975000000000001</v>
+        <v>0.0341</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2636</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0118</v>
+        <v>-0.6032</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4085</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. GARCIA MARTINEZ</t>
+          <t>O. NGOMO MIFUMU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.797</v>
+        <v>0.1996</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0523</v>
+        <v>2.2379</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8493</v>
+        <v>-2.0383</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6351</v>
+        <v>-1.2997</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.371</v>
+        <v>0.4338</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7359</v>
+        <v>-1.7334</v>
       </c>
       <c r="J6" t="n">
-        <v>0.257</v>
+        <v>2.5609</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.589</v>
+        <v>2.4353</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8459</v>
+        <v>0.1256</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8921</v>
+        <v>-3.8605</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.782</v>
+        <v>-2.0015</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.11</v>
+        <v>-1.859</v>
       </c>
       <c r="P6" t="n">
         <v>0.7935</v>
@@ -922,22 +922,22 @@
         <v>1.7855</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2418</v>
+        <v>0.7057</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3173</v>
+        <v>0.669</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5591</v>
+        <v>0.0368</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3097</v>
+        <v>-1.7231</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3258</v>
+        <v>0.6318</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6355</v>
+        <v>-2.3549</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2749</v>
@@ -1000,13 +1000,13 @@
         <v>1.5871</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6381</v>
+        <v>-1.0514</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8728</v>
+        <v>-0.5667</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7652</v>
+        <v>-0.4847</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
+          <t>A. ROSA BEJARANO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5457</v>
+        <v>-1.98</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.481</v>
+        <v>-0.5815</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0646</v>
+        <v>-1.3984</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.153</v>
+        <v>-0.9644</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.648</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4949</v>
+        <v>-0.9548</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2397</v>
+        <v>0.8128</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3201</v>
+        <v>0.8478</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0803</v>
+        <v>-0.0351</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0867</v>
+        <v>-1.7772</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3279</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4146</v>
+        <v>-0.9198</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7935</v>
+        <v>0.3968</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1984</v>
+        <v>1.3887</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5991</v>
+        <v>-0.8091</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2494</v>
+        <v>-0.4024</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3498</v>
+        <v>-0.4068</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ROSA BEJARANO</t>
+          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6531</v>
+        <v>-2.4553</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1143</v>
+        <v>-2.4187</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5387</v>
+        <v>-0.0366</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9644</v>
+        <v>-1.153</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-1.648</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9548</v>
+        <v>0.4949</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8128</v>
+        <v>-1.2397</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8478</v>
+        <v>-1.3201</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0351</v>
+        <v>0.0803</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7772</v>
+        <v>0.0867</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.3279</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9198</v>
+        <v>0.4146</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3968</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3887</v>
+        <v>0.1984</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4822</v>
+        <v>-0.5087</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9352</v>
+        <v>-0.187</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.547</v>
+        <v>-0.3217</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.339</v>
+        <v>-4.6975</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4074</v>
+        <v>0.4698</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.7465</v>
+        <v>-5.1673</v>
       </c>
       <c r="G10" t="n">
         <v>-5.4325</v>
@@ -1234,13 +1234,13 @@
         <v>1.3887</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0935</v>
+        <v>-0.265</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1926</v>
+        <v>-0.1303</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2862</v>
+        <v>-0.1347</v>
       </c>
       <c r="V10" t="n">
         <v>0.6032</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.1731</v>
+        <v>-4.9424</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7106</v>
+        <v>-0.6482</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.4625</v>
+        <v>-4.2942</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4748</v>
@@ -1312,13 +1312,13 @@
         <v>1.5871</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.095</v>
+        <v>-0.8643999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.255</v>
+        <v>-0.1926</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8401</v>
+        <v>-0.6717</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2065</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.983099999999999</v>
+        <v>-6.424499999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>4.718</v>
+        <v>6.2768</v>
       </c>
       <c r="F12" t="n">
-        <v>-12.7011</v>
+        <v>-12.701</v>
       </c>
       <c r="G12" t="n">
         <v>-8.162100000000001</v>
@@ -1360,7 +1360,7 @@
         <v>-10.1054</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9431</v>
+        <v>1.943100000000001</v>
       </c>
       <c r="J12" t="n">
         <v>15.3625</v>
@@ -1378,7 +1378,7 @@
         <v>-15.6548</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.869800000000001</v>
+        <v>-7.869799999999999</v>
       </c>
       <c r="P12" t="n">
         <v>1.9838</v>
@@ -1390,16 +1390,16 @@
         <v>14.8791</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.5505</v>
+        <v>-0.9918999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.238</v>
+        <v>-0.6793999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3123999999999999</v>
+        <v>-0.3125999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7458</v>
+        <v>0.7458000000000002</v>
       </c>
       <c r="W12" t="n">
         <v>4.4886</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>,. VICENTE SABARIEGO</t>
+          <t>S. SERRATACO SANCHEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.0099</v>
+        <v>4.3024</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9072</v>
+        <v>5.9052</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1028</v>
+        <v>-1.6028</v>
       </c>
       <c r="G13" t="n">
-        <v>5.9731</v>
+        <v>3.9225</v>
       </c>
       <c r="H13" t="n">
-        <v>5.9731</v>
+        <v>3.9458</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-0.0232</v>
       </c>
       <c r="J13" t="n">
-        <v>5.9731</v>
+        <v>6.7457</v>
       </c>
       <c r="K13" t="n">
-        <v>5.9731</v>
+        <v>4.6573</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.0884</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-2.8232</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>-0.7116</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>-2.1116</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.9758</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.9758</v>
+        <v>-2.1822</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.7855</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3498</v>
+        <v>0.316</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0406</v>
+        <v>0.2778</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3092</v>
+        <v>0.0381</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3373</v>
+        <v>0.4607</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8692</v>
+        <v>1.0639</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2065</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. SERRATACO SANCHEZ</t>
+          <t>,. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7386</v>
+        <v>4.2245</v>
       </c>
       <c r="E14" t="n">
-        <v>6.3134</v>
+        <v>4.6828</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5748</v>
+        <v>-0.4583</v>
       </c>
       <c r="G14" t="n">
-        <v>3.9225</v>
+        <v>5.9731</v>
       </c>
       <c r="H14" t="n">
-        <v>3.9458</v>
+        <v>5.9731</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0232</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>6.7457</v>
+        <v>5.9731</v>
       </c>
       <c r="K14" t="n">
-        <v>4.6573</v>
+        <v>5.9731</v>
       </c>
       <c r="L14" t="n">
-        <v>2.0884</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.8232</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7116</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.1116</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3968</v>
+        <v>-2.9758</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1822</v>
+        <v>-2.9758</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7855</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7521</v>
+        <v>1.5644</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6859</v>
+        <v>0.8162</v>
       </c>
       <c r="U14" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.7481</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4607</v>
+        <v>-0.3373</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0639</v>
+        <v>0.8692</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6032</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4781</v>
+        <v>3.381</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6881</v>
+        <v>4.1983</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.21</v>
+        <v>-0.8172</v>
       </c>
       <c r="G15" t="n">
         <v>1.9904</v>
@@ -1624,13 +1624,13 @@
         <v>1.3887</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9171</v>
+        <v>-0.0142</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5498</v>
+        <v>-0.0396</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3673</v>
+        <v>0.0254</v>
       </c>
       <c r="V15" t="n">
         <v>1.2065</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6856</v>
+        <v>2.1141</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5363</v>
+        <v>1.7403</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1493</v>
+        <v>0.3738</v>
       </c>
       <c r="G16" t="n">
         <v>1.2611</v>
@@ -1702,13 +1702,13 @@
         <v>0.7935</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7063</v>
+        <v>-0.2778</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3627</v>
+        <v>-0.1587</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3435</v>
+        <v>-0.1191</v>
       </c>
       <c r="V16" t="n">
         <v>0.3373</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.406</v>
+        <v>0.9979</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6076</v>
+        <v>1.1995</v>
       </c>
       <c r="F17" t="n">
         <v>-0.2016</v>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6802</v>
+        <v>0.2721</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6802</v>
+        <v>0.2721</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8427</v>
+        <v>0.9549</v>
       </c>
       <c r="E18" t="n">
         <v>-0.8557</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6985</v>
+        <v>1.8107</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8419</v>
@@ -1858,13 +1858,13 @@
         <v>1.5871</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2959</v>
+        <v>0.4081</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1076</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4035</v>
+        <v>0.5157</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5128</v>
+        <v>0.0665</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2795</v>
+        <v>-0.5856</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7924</v>
+        <v>0.6521</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9807</v>
@@ -1936,13 +1936,13 @@
         <v>0.7935</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7</v>
+        <v>0.2537</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3175</v>
+        <v>0.0114</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3825</v>
+        <v>0.2423</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1955,11 +1955,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>D. TUGORES SOTO</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -1969,58 +1965,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8055</v>
+        <v>-0.6864</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8705000000000001</v>
+        <v>0.6815</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9351</v>
+        <v>-1.3678</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4617</v>
+        <v>-3.1832</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8413</v>
+        <v>-1.306</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3796</v>
+        <v>-1.8771</v>
       </c>
       <c r="J20" t="n">
-        <v>3.1651</v>
+        <v>0.6644</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1545</v>
+        <v>0.4234</v>
       </c>
       <c r="L20" t="n">
-        <v>2.0106</v>
+        <v>0.241</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7034</v>
+        <v>-3.8475</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3132</v>
+        <v>-1.7294</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.3902</v>
+        <v>-2.1181</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.7774</v>
+        <v>2.1822</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.1661</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3887</v>
+        <v>2.1822</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5101</v>
+        <v>0.3146</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1304</v>
+        <v>0.0171</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3797</v>
+        <v>0.2975</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2033,7 +2029,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>. VICENTE SABARIEGO</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -2043,13 +2043,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8954</v>
+        <v>-0.6864</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1348</v>
+        <v>0.6815</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7606</v>
+        <v>-1.3678</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1832</v>
@@ -2088,13 +2088,13 @@
         <v>2.1822</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8944</v>
+        <v>0.3146</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7991</v>
+        <v>0.0171</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0953</v>
+        <v>0.2975</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>. VICENTE SABARIEGO</t>
+          <t>E. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2121,73 +2121,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8954</v>
+        <v>-1.7379</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1348</v>
+        <v>0.2989</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7606</v>
+        <v>-2.0368</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.1832</v>
+        <v>1.3939</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.306</v>
+        <v>0.8718</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.8771</v>
+        <v>0.5221</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6644</v>
+        <v>3.8697</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4234</v>
+        <v>2.0522</v>
       </c>
       <c r="L22" t="n">
-        <v>0.241</v>
+        <v>1.8175</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.8475</v>
+        <v>-2.4758</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7294</v>
+        <v>-1.1804</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.1181</v>
+        <v>-1.2954</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1822</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.1741</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1822</v>
+        <v>1.7855</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8944</v>
+        <v>0.0665</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7991</v>
+        <v>-0.3967</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0953</v>
+        <v>0.4632</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.8097</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. MAÑES CARRETERO</t>
+          <t>D. TUGORES SOTO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2199,67 +2199,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0874</v>
+        <v>-1.8055</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4153</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6721</v>
+        <v>-0.9351</v>
       </c>
       <c r="G23" t="n">
-        <v>1.3939</v>
+        <v>0.4617</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8718</v>
+        <v>0.8413</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5221</v>
+        <v>-0.3796</v>
       </c>
       <c r="J23" t="n">
-        <v>3.8697</v>
+        <v>3.1651</v>
       </c>
       <c r="K23" t="n">
-        <v>2.0522</v>
+        <v>1.1545</v>
       </c>
       <c r="L23" t="n">
-        <v>1.8175</v>
+        <v>2.0106</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.4758</v>
+        <v>-2.7034</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1804</v>
+        <v>-0.3132</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2954</v>
+        <v>-2.3902</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3887</v>
+        <v>-2.7774</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.1741</v>
+        <v>-4.1661</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2829</v>
+        <v>0.5101</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1109</v>
+        <v>0.1304</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8279</v>
+        <v>0.3797</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.8097</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.8097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2277,13 +2277,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9025</v>
+        <v>-3.2418</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7956</v>
+        <v>-3.3875</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1068</v>
+        <v>0.1457</v>
       </c>
       <c r="G24" t="n">
         <v>-2.5607</v>
@@ -2322,13 +2322,13 @@
         <v>1.1903</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9369</v>
+        <v>-0.2763</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6121</v>
+        <v>-0.204</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3248</v>
+        <v>-0.0723</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6032</v>
@@ -2355,13 +2355,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.087499999999999</v>
+        <v>7.883299999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>12.56640000000001</v>
+        <v>13.6887</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.4786</v>
+        <v>-5.8051</v>
       </c>
       <c r="G25" t="n">
         <v>4.978800000000001</v>
@@ -2370,7 +2370,7 @@
         <v>8.799200000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.82</v>
+        <v>-3.819999999999999</v>
       </c>
       <c r="J25" t="n">
         <v>24.1889</v>
@@ -2379,7 +2379,7 @@
         <v>16.0782</v>
       </c>
       <c r="L25" t="n">
-        <v>8.110799999999998</v>
+        <v>8.110800000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-19.2099</v>
@@ -2400,13 +2400,13 @@
         <v>15.0772</v>
       </c>
       <c r="S25" t="n">
-        <v>1.656099999999999</v>
+        <v>3.4518</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4867000000000009</v>
+        <v>0.6354999999999998</v>
       </c>
       <c r="U25" t="n">
-        <v>2.1428</v>
+        <v>2.8161</v>
       </c>
       <c r="V25" t="n">
         <v>-0.7457000000000003</v>
